--- a/artfynd/A 26473-2026 artfynd.xlsx
+++ b/artfynd/A 26473-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111947493</v>
+        <v>111947485</v>
       </c>
       <c r="B2" t="n">
-        <v>78746</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534492</v>
+        <v>534372</v>
       </c>
       <c r="R2" t="n">
-        <v>7039781</v>
+        <v>7040050</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111947495</v>
+        <v>111947486</v>
       </c>
       <c r="B3" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534464</v>
+        <v>534382</v>
       </c>
       <c r="R3" t="n">
-        <v>7039784</v>
+        <v>7040140</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111947482</v>
+        <v>111947496</v>
       </c>
       <c r="B4" t="n">
-        <v>77403</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534278</v>
+        <v>534488</v>
       </c>
       <c r="R4" t="n">
-        <v>7040038</v>
+        <v>7039790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111947483</v>
+        <v>56077579</v>
       </c>
       <c r="B5" t="n">
-        <v>77402</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,7 +1004,7 @@
         <v>534278</v>
       </c>
       <c r="R5" t="n">
-        <v>7040038</v>
+        <v>7040192</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2013-05-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2013-05-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1051,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111947496</v>
+        <v>56077578</v>
       </c>
       <c r="B6" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1078,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Störåsen, Jmt</t>
+          <t>N Störåsberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534488</v>
+        <v>534304</v>
       </c>
       <c r="R6" t="n">
-        <v>7039790</v>
+        <v>7040001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2013-05-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2013-05-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,27 +1152,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111947491</v>
+        <v>111947483</v>
       </c>
       <c r="B7" t="n">
-        <v>78242</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1179,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534427</v>
+        <v>534278</v>
       </c>
       <c r="R7" t="n">
-        <v>7039928</v>
+        <v>7040038</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1265,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111947488</v>
+        <v>111947490</v>
       </c>
       <c r="B8" t="n">
-        <v>78647</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534414</v>
+        <v>534428</v>
       </c>
       <c r="R8" t="n">
-        <v>7040098</v>
+        <v>7039928</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,37 +1362,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111947485</v>
+        <v>111947484</v>
       </c>
       <c r="B9" t="n">
-        <v>89517</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534372</v>
+        <v>534278</v>
       </c>
       <c r="R9" t="n">
-        <v>7040050</v>
+        <v>7040038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111947492</v>
+        <v>111947491</v>
       </c>
       <c r="B10" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1470,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534568</v>
+        <v>534428</v>
       </c>
       <c r="R10" t="n">
-        <v>7039895</v>
+        <v>7039928</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,37 +1556,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111947486</v>
+        <v>111947488</v>
       </c>
       <c r="B11" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534382</v>
+        <v>534414</v>
       </c>
       <c r="R11" t="n">
-        <v>7040140</v>
+        <v>7040098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,15 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111947489</v>
+        <v>56077575</v>
       </c>
       <c r="B12" t="n">
-        <v>90858</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,34 +1664,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Störåsen, Jmt</t>
+          <t>N Störåsberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534412</v>
+        <v>534247</v>
       </c>
       <c r="R12" t="n">
-        <v>7040073</v>
+        <v>7039946</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,12 +1718,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2013-05-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2013-05-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,27 +1738,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111947487</v>
+        <v>56077580</v>
       </c>
       <c r="B13" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,10 +1789,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>534382</v>
+        <v>534383</v>
       </c>
       <c r="R13" t="n">
-        <v>7040140</v>
+        <v>7040195</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,12 +1819,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2013-05-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2013-05-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,49 +1839,48 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111947494</v>
+        <v>111947487</v>
       </c>
       <c r="B14" t="n">
-        <v>78740</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>534492</v>
+        <v>534382</v>
       </c>
       <c r="R14" t="n">
-        <v>7039781</v>
+        <v>7040140</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,15 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111947484</v>
+        <v>111947495</v>
       </c>
       <c r="B15" t="n">
-        <v>78242</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +1963,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>534278</v>
+        <v>534464</v>
       </c>
       <c r="R15" t="n">
-        <v>7040038</v>
+        <v>7039784</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,37 +2049,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111947490</v>
+        <v>111947494</v>
       </c>
       <c r="B16" t="n">
-        <v>77402</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>534427</v>
+        <v>534492</v>
       </c>
       <c r="R16" t="n">
-        <v>7039928</v>
+        <v>7039781</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,6 +2143,200 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>111947493</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>534492</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7039781</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>111947482</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Störåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>534278</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7040038</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26473-2026 artfynd.xlsx
+++ b/artfynd/A 26473-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947485</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947486</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947496</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56077579</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56077578</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947483</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947490</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947484</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947491</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947488</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1751,6 +1806,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56077575</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1852,6 +1912,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56077580</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1949,6 +2014,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947487</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2046,6 +2116,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947495</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2143,6 +2218,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947494</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2240,6 +2320,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947493</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2337,8 +2422,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947482</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>